--- a/marketer_forms/005_social_media_insights_request_form--marketer_forms.xlsx
+++ b/marketer_forms/005_social_media_insights_request_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'account_level_insights',_'label':_'account_level_insights'}</t>
+          <t>account_level_insights</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'account_level_insights', 'label': 'Account Level Insights'}</t>
+          <t>Account Level Insights</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'campaign_level_insights',_'label':_'campaign_level_insights'}</t>
+          <t>campaign_level_insights</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'campaign_level_insights', 'label': 'Campaign Level Insights'}</t>
+          <t>Campaign Level Insights</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'post_level_insights',_'label':_'post_level_insights'}</t>
+          <t>post_level_insights</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'post_level_insights', 'label': 'Post Level Insights'}</t>
+          <t>Post Level Insights</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'user_level_insights',_'label':_'user_level_insights'}</t>
+          <t>user_level_insights</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'user_level_insights', 'label': 'User Level Insights'}</t>
+          <t>User Level Insights</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
